--- a/docs/design-docs/08_プログラム設計書_マスタ管理.xlsx
+++ b/docs/design-docs/08_プログラム設計書_マスタ管理.xlsx
@@ -13,7 +13,656 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="216">
+  <si>
+    <t>版数</t>
+  </si>
+  <si>
+    <t>改訂日</t>
+  </si>
+  <si>
+    <t>改訂内容</t>
+  </si>
+  <si>
+    <t>改訂者</t>
+  </si>
+  <si>
+    <t>承認者</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>2026/05/23</t>
+  </si>
+  <si>
+    <t>初版作成</t>
+  </si>
+  <si>
+    <t>システム開発部</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>新規</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 設備マスタ一覧</t>
+  </si>
+  <si>
+    <t>文書管理情報</t>
+  </si>
+  <si>
+    <t>システムID</t>
+  </si>
+  <si>
+    <t>STRUTSLAB-001</t>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+  </si>
+  <si>
+    <t>マスタ管理</t>
+  </si>
+  <si>
+    <t>プログラムID</t>
+  </si>
+  <si>
+    <t>PG-MST-EQP-001</t>
+  </si>
+  <si>
+    <t>プログラム名</t>
+  </si>
+  <si>
+    <t>設備マスタ一覧</t>
+  </si>
+  <si>
+    <t>文書番号</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-MST-EQP-001</t>
+  </si>
+  <si>
+    <t>作成日</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>プログラム概要</t>
+  </si>
+  <si>
+    <t>設備マスタの検索・一覧表示。複合検索(5条件AND)、paging、CSV出力、選択削除。session scopeで検索条件保持。</t>
+  </si>
+  <si>
+    <t>入出力定義</t>
+  </si>
+  <si>
+    <t>項目名</t>
+  </si>
+  <si>
+    <t>型</t>
+  </si>
+  <si>
+    <t>Formプロパティ</t>
+  </si>
+  <si>
+    <t>必須</t>
+  </si>
+  <si>
+    <t>入力</t>
+  </si>
+  <si>
+    <t>設備種別</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>eqpSearchType</t>
+  </si>
+  <si>
+    <t>select</t>
+  </si>
+  <si>
+    <t>電圧階級</t>
+  </si>
+  <si>
+    <t>eqpSearchVoltage</t>
+  </si>
+  <si>
+    <t>設置年from/to</t>
+  </si>
+  <si>
+    <t>eqpSearchYearFrom/To</t>
+  </si>
+  <si>
+    <t>保全ランク</t>
+  </si>
+  <si>
+    <t>eqpSearchRank</t>
+  </si>
+  <si>
+    <t>担当部署</t>
+  </si>
+  <si>
+    <t>eqpSearchDept</t>
+  </si>
+  <si>
+    <t>部分一致</t>
+  </si>
+  <si>
+    <t>出力</t>
+  </si>
+  <si>
+    <t>検索結果</t>
+  </si>
+  <si>
+    <t>List&amp;lt;EqpDto&amp;gt;</t>
+  </si>
+  <si>
+    <t>eqpList</t>
+  </si>
+  <si>
+    <t>処理詳細</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>処理内容</t>
+  </si>
+  <si>
+    <t>関連DAO</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Form値→検索条件DTO構築(未入力条件null→WHERE除外)</t>
+  </si>
+  <si>
+    <t>MyBatis &amp;lt;if&amp;gt;動的SQL</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>DAO.search()実行</t>
+  </si>
+  <si>
+    <t>EqpDao.search()</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>paging: 総件数→offset計算</t>
+  </si>
+  <si>
+    <t>EqpDao.count()</t>
+  </si>
+  <si>
+    <t>LIMIT/OFFSET</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Request属性設定→JSP描画</t>
+  </si>
+  <si>
+    <t>入力検証ルール</t>
+  </si>
+  <si>
+    <t>対象項目</t>
+  </si>
+  <si>
+    <t>検証ルール</t>
+  </si>
+  <si>
+    <t>エラーメッセージ(ja)</t>
+  </si>
+  <si>
+    <t>YYYY形式, from≦to</t>
+  </si>
+  <si>
+    <t>設置年の範囲が正しくありません</t>
+  </si>
+  <si>
+    <t>最大50文字</t>
+  </si>
+  <si>
+    <t>状態遷移</t>
+  </si>
+  <si>
+    <t>遷移元</t>
+  </si>
+  <si>
+    <t>遷移先</t>
+  </si>
+  <si>
+    <t>トリガー</t>
+  </si>
+  <si>
+    <t>一覧</t>
+  </si>
+  <si>
+    <t>検索結果表示</t>
+  </si>
+  <si>
+    <t>検索/クリア</t>
+  </si>
+  <si>
+    <t>CSV出力</t>
+  </si>
+  <si>
+    <t>編集画面</t>
+  </si>
+  <si>
+    <t>click</t>
+  </si>
+  <si>
+    <t>削除→再表示</t>
+  </si>
+  <si>
+    <t>選択削除+confirm</t>
+  </si>
+  <si>
+    <t>struts-config.xml</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>値</t>
+  </si>
+  <si>
+    <t>action path</t>
+  </si>
+  <si>
+    <t>/mst/eqp/list</t>
+  </si>
+  <si>
+    <t>action class</t>
+  </si>
+  <si>
+    <t>EqpListAction</t>
+  </si>
+  <si>
+    <t>form bean</t>
+  </si>
+  <si>
+    <t>EqpSearchForm</t>
+  </si>
+  <si>
+    <t>scope</t>
+  </si>
+  <si>
+    <t>session</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 設備マスタ登録・編集</t>
+  </si>
+  <si>
+    <t>PG-MST-EQP-002</t>
+  </si>
+  <si>
+    <t>設備マスタ登録・編集</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-MST-EQP-002</t>
+  </si>
+  <si>
+    <t>設備マスタの新規登録・編集。5section大form、親設備Popup選択、添付file処理。DispatchAction。</t>
+  </si>
+  <si>
+    <t>設備名</t>
+  </si>
+  <si>
+    <t>eqpName</t>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
+    <t>eqpType</t>
+  </si>
+  <si>
+    <t>設備status</t>
+  </si>
+  <si>
+    <t>eqpStatus</t>
+  </si>
+  <si>
+    <t>eqpVoltage</t>
+  </si>
+  <si>
+    <t>親設備code</t>
+  </si>
+  <si>
+    <t>eqpParentCode</t>
+  </si>
+  <si>
+    <t>Popup</t>
+  </si>
+  <si>
+    <t>eqpRank</t>
+  </si>
+  <si>
+    <t>点検周期</t>
+  </si>
+  <si>
+    <t>Integer</t>
+  </si>
+  <si>
+    <t>eqpInterval</t>
+  </si>
+  <si>
+    <t>1-120</t>
+  </si>
+  <si>
+    <t>添付file</t>
+  </si>
+  <si>
+    <t>FormFile</t>
+  </si>
+  <si>
+    <t>eqpFile</t>
+  </si>
+  <si>
+    <t>編集時 既存data取得(新規skip)</t>
+  </si>
+  <si>
+    <t>EqpDao.findById()</t>
+  </si>
+  <si>
+    <t>Form→DTO→Validator</t>
+  </si>
+  <si>
+    <t>error時INPUT</t>
+  </si>
+  <si>
+    <t>親設備存在+状態check(廃止不可)</t>
+  </si>
+  <si>
+    <t>新規:insert/編集:update</t>
+  </si>
+  <si>
+    <t>EqpDao</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>添付file→filesystem</t>
+  </si>
+  <si>
+    <t>/attachments/eqp/</t>
+  </si>
+  <si>
+    <t>空不可 max100</t>
+  </si>
+  <si>
+    <t>設備名を入力してください</t>
+  </si>
+  <si>
+    <t>空不可</t>
+  </si>
+  <si>
+    <t>1〜120</t>
+  </si>
+  <si>
+    <t>点検周期は1〜120ヶ月</t>
+  </si>
+  <si>
+    <t>廃止不可</t>
+  </si>
+  <si>
+    <t>max10MB pdf/jpg/png</t>
+  </si>
+  <si>
+    <t>表示</t>
+  </si>
+  <si>
+    <t>編集中</t>
+  </si>
+  <si>
+    <t>error→再表示</t>
+  </si>
+  <si>
+    <t>保存→NG</t>
+  </si>
+  <si>
+    <t>保存→OK</t>
+  </si>
+  <si>
+    <t>選択</t>
+  </si>
+  <si>
+    <t>/mst/eqp/save</t>
+  </si>
+  <si>
+    <t>EqpSaveAction(DispatchAction)</t>
+  </si>
+  <si>
+    <t>EqpForm(ValidatorForm)</t>
+  </si>
+  <si>
+    <t>request</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 点検項目マスタ一覧</t>
+  </si>
+  <si>
+    <t>PG-MST-CHK-001</t>
+  </si>
+  <si>
+    <t>点検項目マスタ一覧</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-MST-CHK-001</t>
+  </si>
+  <si>
+    <t>点検項目templateの検索・一覧。template copy、並順変更(sort_order swap)。</t>
+  </si>
+  <si>
+    <t>chkSearchType</t>
+  </si>
+  <si>
+    <t>点検種別</t>
+  </si>
+  <si>
+    <t>chkSearchKind</t>
+  </si>
+  <si>
+    <t>template list</t>
+  </si>
+  <si>
+    <t>List&amp;lt;ChkTmplDto&amp;gt;</t>
+  </si>
+  <si>
+    <t>tmplList</t>
+  </si>
+  <si>
+    <t>検索条件→DAO.search()</t>
+  </si>
+  <si>
+    <t>ChkItemDao.search()</t>
+  </si>
+  <si>
+    <t>並順変更:指定行と前後行sort_order swap</t>
+  </si>
+  <si>
+    <t>ChkItemDao.swapOrder()</t>
+  </si>
+  <si>
+    <t>copy:名称「_コピー」付加→全項目複製</t>
+  </si>
+  <si>
+    <t>ChkItemDao.copy()</t>
+  </si>
+  <si>
+    <t>重複時「_コピー2」</t>
+  </si>
+  <si>
+    <t>空可</t>
+  </si>
+  <si>
+    <t>検索</t>
+  </si>
+  <si>
+    <t>並順変更→再表示</t>
+  </si>
+  <si>
+    <t>▲/▼</t>
+  </si>
+  <si>
+    <t>copy→再表示</t>
+  </si>
+  <si>
+    <t>copy</t>
+  </si>
+  <si>
+    <t>編集</t>
+  </si>
+  <si>
+    <t>/mst/chkitem/list</t>
+  </si>
+  <si>
+    <t>CheckItemListAction</t>
+  </si>
+  <si>
+    <t>CheckItemSearchForm</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 点検項目マスタ登録編集</t>
+  </si>
+  <si>
+    <t>PG-MST-CHK-002</t>
+  </si>
+  <si>
+    <t>点検項目マスタ登録編集</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-MST-CHK-002</t>
+  </si>
+  <si>
+    <t>点検項目templateの3階層tree編集。大分類→中分類→個別項目の動的行追加/削除(Submit→再描画)。Indexed+Nested。</t>
+  </si>
+  <si>
+    <t>template名</t>
+  </si>
+  <si>
+    <t>tmplName</t>
+  </si>
+  <si>
+    <t>checkKind</t>
+  </si>
+  <si>
+    <t>大分類[{n}].name</t>
+  </si>
+  <si>
+    <t>String[]</t>
+  </si>
+  <si>
+    <t>cat1Names</t>
+  </si>
+  <si>
+    <t>Indexed</t>
+  </si>
+  <si>
+    <t>中分類[{n}][{m}]</t>
+  </si>
+  <si>
+    <t>String[][]</t>
+  </si>
+  <si>
+    <t>cat2Names</t>
+  </si>
+  <si>
+    <t>Nested</t>
+  </si>
+  <si>
+    <t>項目[{i}].*</t>
+  </si>
+  <si>
+    <t>ItemDto[]</t>
+  </si>
+  <si>
+    <t>items</t>
+  </si>
+  <si>
+    <t>動的行操作判定(addRow/delRow/save)</t>
+  </si>
+  <si>
+    <t>行追加:配列size+1→空data→INPUT forward</t>
+  </si>
+  <si>
+    <t>既存行index維持</t>
+  </si>
+  <si>
+    <t>行削除:指定index除去→詰直</t>
+  </si>
+  <si>
+    <t>保存:3階層→transaction</t>
+  </si>
+  <si>
+    <t>ChkItemDao</t>
+  </si>
+  <si>
+    <t>大→中→項目順</t>
+  </si>
+  <si>
+    <t>空不可 重複不可</t>
+  </si>
+  <si>
+    <t>cat1Names[{n}]</t>
+  </si>
+  <si>
+    <t>items[{i}].name</t>
+  </si>
+  <si>
+    <t>行追加→再表示</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>行削除→再表示</t>
+  </si>
+  <si>
+    <t>削除</t>
+  </si>
+  <si>
+    <t>保存→一覧</t>
+  </si>
+  <si>
+    <t>保存</t>
+  </si>
+  <si>
+    <t>一括追加</t>
+  </si>
+  <si>
+    <t>一括項目追加</t>
+  </si>
+  <si>
+    <t>/mst/chkitem/save</t>
+  </si>
+  <si>
+    <t>CheckItemSaveAction</t>
+  </si>
+  <si>
+    <t>CheckItemForm(ValidatorForm)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
